--- a/docs/Results/Dual_All_Scenarios/dual_benefit_state_stats_ALL.xlsx
+++ b/docs/Results/Dual_All_Scenarios/dual_benefit_state_stats_ALL.xlsx
@@ -2525,7 +2525,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Hessen (Regular)</t>
+          <t>Bayern (Regular)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2534,16 +2534,16 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>3096</v>
+        <v>2035</v>
       </c>
       <c r="D62" t="n">
-        <v>11.6</v>
+        <v>2.4</v>
       </c>
       <c r="E62" t="n">
-        <v>299988</v>
+        <v>275240</v>
       </c>
       <c r="F62" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Hessen (Regular)</t>
+          <t>Bayern (Regular)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2568,16 +2568,16 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>4410</v>
+        <v>11481</v>
       </c>
       <c r="D63" t="n">
-        <v>16.5</v>
+        <v>13.4</v>
       </c>
       <c r="E63" t="n">
-        <v>464075</v>
+        <v>1234440</v>
       </c>
       <c r="F63" t="n">
-        <v>7.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Hessen (Regular)</t>
+          <t>Bayern (Regular)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2602,16 +2602,16 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>7164</v>
+        <v>21797</v>
       </c>
       <c r="D64" t="n">
-        <v>26.8</v>
+        <v>25.4</v>
       </c>
       <c r="E64" t="n">
-        <v>1230482</v>
+        <v>3083180</v>
       </c>
       <c r="F64" t="n">
-        <v>19.7</v>
+        <v>23.2</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Hessen (Regular)</t>
+          <t>Bayern (Regular)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2636,16 +2636,16 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>185</v>
+        <v>159</v>
       </c>
       <c r="D65" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="E65" t="n">
-        <v>6027</v>
+        <v>2872</v>
       </c>
       <c r="F65" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Hessen (Regular)</t>
+          <t>Bayern (Regular)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2670,16 +2670,16 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0</v>
+        <v>2186</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>15199</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Hessen (Regular)</t>
+          <t>Bayern (Regular)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2704,16 +2704,16 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>11893</v>
+        <v>48035</v>
       </c>
       <c r="D67" t="n">
-        <v>44.5</v>
+        <v>56.1</v>
       </c>
       <c r="E67" t="n">
-        <v>4253838</v>
+        <v>8660199</v>
       </c>
       <c r="F67" t="n">
-        <v>68</v>
+        <v>65.3</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Hessen (Extended)</t>
+          <t>Bayern (Extended)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2738,16 +2738,16 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1438</v>
+        <v>1268</v>
       </c>
       <c r="D68" t="n">
-        <v>5.4</v>
+        <v>1.5</v>
       </c>
       <c r="E68" t="n">
-        <v>141136</v>
+        <v>208993</v>
       </c>
       <c r="F68" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Hessen (Extended)</t>
+          <t>Bayern (Extended)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2772,16 +2772,16 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>3440</v>
+        <v>9597</v>
       </c>
       <c r="D69" t="n">
-        <v>12.9</v>
+        <v>11.2</v>
       </c>
       <c r="E69" t="n">
-        <v>359958</v>
+        <v>1035285</v>
       </c>
       <c r="F69" t="n">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Hessen (Extended)</t>
+          <t>Bayern (Extended)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2806,16 +2806,16 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>7699</v>
+        <v>20907</v>
       </c>
       <c r="D70" t="n">
-        <v>28.8</v>
+        <v>24.4</v>
       </c>
       <c r="E70" t="n">
-        <v>1086857</v>
+        <v>2984116</v>
       </c>
       <c r="F70" t="n">
-        <v>17.4</v>
+        <v>22.5</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Hessen (Extended)</t>
+          <t>Bayern (Extended)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2840,13 +2840,13 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="D71" t="n">
         <v>0.1</v>
       </c>
       <c r="E71" t="n">
-        <v>677</v>
+        <v>2188</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
@@ -2865,7 +2865,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Hessen (Extended)</t>
+          <t>Bayern (Extended)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2874,16 +2874,16 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>0</v>
+        <v>2186</v>
       </c>
       <c r="D72" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>15199</v>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Hessen (Extended)</t>
+          <t>Bayern (Extended)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2908,16 +2908,16 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>14134</v>
+        <v>51657</v>
       </c>
       <c r="D73" t="n">
-        <v>52.8</v>
+        <v>60.3</v>
       </c>
       <c r="E73" t="n">
-        <v>4665782</v>
+        <v>9025349</v>
       </c>
       <c r="F73" t="n">
-        <v>74.59999999999999</v>
+        <v>68</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Bayern (Regular)</t>
+          <t>Hessen (Regular)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2942,16 +2942,16 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>2035</v>
+        <v>3096</v>
       </c>
       <c r="D74" t="n">
-        <v>2.4</v>
+        <v>11.6</v>
       </c>
       <c r="E74" t="n">
-        <v>275240</v>
+        <v>299988</v>
       </c>
       <c r="F74" t="n">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Bayern (Regular)</t>
+          <t>Hessen (Regular)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2976,16 +2976,16 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>11481</v>
+        <v>4410</v>
       </c>
       <c r="D75" t="n">
-        <v>13.4</v>
+        <v>16.5</v>
       </c>
       <c r="E75" t="n">
-        <v>1234440</v>
+        <v>464075</v>
       </c>
       <c r="F75" t="n">
-        <v>9.300000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Bayern (Regular)</t>
+          <t>Hessen (Regular)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3010,16 +3010,16 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>21797</v>
+        <v>7164</v>
       </c>
       <c r="D76" t="n">
-        <v>25.4</v>
+        <v>26.8</v>
       </c>
       <c r="E76" t="n">
-        <v>3083180</v>
+        <v>1230482</v>
       </c>
       <c r="F76" t="n">
-        <v>23.2</v>
+        <v>19.7</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Bayern (Regular)</t>
+          <t>Hessen (Regular)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3044,16 +3044,16 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="D77" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="E77" t="n">
-        <v>2872</v>
+        <v>6027</v>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Bayern (Regular)</t>
+          <t>Hessen (Regular)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3078,16 +3078,16 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>2186</v>
+        <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>15199</v>
+        <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Bayern (Regular)</t>
+          <t>Hessen (Regular)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3112,16 +3112,16 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>48035</v>
+        <v>11893</v>
       </c>
       <c r="D79" t="n">
-        <v>56.1</v>
+        <v>44.5</v>
       </c>
       <c r="E79" t="n">
-        <v>8660199</v>
+        <v>4253838</v>
       </c>
       <c r="F79" t="n">
-        <v>65.3</v>
+        <v>68</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Bayern (Extended)</t>
+          <t>Hessen (Extended)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3146,16 +3146,16 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1268</v>
+        <v>1438</v>
       </c>
       <c r="D80" t="n">
-        <v>1.5</v>
+        <v>5.4</v>
       </c>
       <c r="E80" t="n">
-        <v>208993</v>
+        <v>141136</v>
       </c>
       <c r="F80" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Bayern (Extended)</t>
+          <t>Hessen (Extended)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3180,16 +3180,16 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>9597</v>
+        <v>3440</v>
       </c>
       <c r="D81" t="n">
-        <v>11.2</v>
+        <v>12.9</v>
       </c>
       <c r="E81" t="n">
-        <v>1035285</v>
+        <v>359958</v>
       </c>
       <c r="F81" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Bayern (Extended)</t>
+          <t>Hessen (Extended)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3214,16 +3214,16 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>20907</v>
+        <v>7699</v>
       </c>
       <c r="D82" t="n">
-        <v>24.4</v>
+        <v>28.8</v>
       </c>
       <c r="E82" t="n">
-        <v>2984116</v>
+        <v>1086857</v>
       </c>
       <c r="F82" t="n">
-        <v>22.5</v>
+        <v>17.4</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Bayern (Extended)</t>
+          <t>Hessen (Extended)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3248,13 +3248,13 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>78</v>
+        <v>37</v>
       </c>
       <c r="D83" t="n">
         <v>0.1</v>
       </c>
       <c r="E83" t="n">
-        <v>2188</v>
+        <v>677</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -3273,7 +3273,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Bayern (Extended)</t>
+          <t>Hessen (Extended)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3282,16 +3282,16 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>2186</v>
+        <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>15199</v>
+        <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Bayern (Extended)</t>
+          <t>Hessen (Extended)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3316,16 +3316,16 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>51657</v>
+        <v>14134</v>
       </c>
       <c r="D85" t="n">
-        <v>60.3</v>
+        <v>52.8</v>
       </c>
       <c r="E85" t="n">
-        <v>9025349</v>
+        <v>4665782</v>
       </c>
       <c r="F85" t="n">
-        <v>68</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -28637,7 +28637,7 @@
     <row r="830">
       <c r="A830" t="inlineStr">
         <is>
-          <t>Bayern (Regular)</t>
+          <t>Hessen (Regular)</t>
         </is>
       </c>
       <c r="B830" t="inlineStr">
@@ -28646,16 +28646,16 @@
         </is>
       </c>
       <c r="C830" t="n">
-        <v>230</v>
+        <v>729</v>
       </c>
       <c r="D830" t="n">
-        <v>0.3</v>
+        <v>2.7</v>
       </c>
       <c r="E830" t="n">
-        <v>9712</v>
+        <v>46046</v>
       </c>
       <c r="F830" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="G830" t="inlineStr">
         <is>
@@ -28671,7 +28671,7 @@
     <row r="831">
       <c r="A831" t="inlineStr">
         <is>
-          <t>Bayern (Regular)</t>
+          <t>Hessen (Regular)</t>
         </is>
       </c>
       <c r="B831" t="inlineStr">
@@ -28680,16 +28680,16 @@
         </is>
       </c>
       <c r="C831" t="n">
-        <v>3511</v>
+        <v>3014</v>
       </c>
       <c r="D831" t="n">
-        <v>4.1</v>
+        <v>11.3</v>
       </c>
       <c r="E831" t="n">
-        <v>197929</v>
+        <v>193787</v>
       </c>
       <c r="F831" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="G831" t="inlineStr">
         <is>
@@ -28705,7 +28705,7 @@
     <row r="832">
       <c r="A832" t="inlineStr">
         <is>
-          <t>Bayern (Regular)</t>
+          <t>Hessen (Regular)</t>
         </is>
       </c>
       <c r="B832" t="inlineStr">
@@ -28714,16 +28714,16 @@
         </is>
       </c>
       <c r="C832" t="n">
-        <v>15607</v>
+        <v>5796</v>
       </c>
       <c r="D832" t="n">
-        <v>18.2</v>
+        <v>21.7</v>
       </c>
       <c r="E832" t="n">
-        <v>1118370</v>
+        <v>488536</v>
       </c>
       <c r="F832" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="G832" t="inlineStr">
         <is>
@@ -28739,7 +28739,7 @@
     <row r="833">
       <c r="A833" t="inlineStr">
         <is>
-          <t>Bayern (Regular)</t>
+          <t>Hessen (Regular)</t>
         </is>
       </c>
       <c r="B833" t="inlineStr">
@@ -28748,16 +28748,16 @@
         </is>
       </c>
       <c r="C833" t="n">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="D833" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="E833" t="n">
-        <v>2851</v>
+        <v>6027</v>
       </c>
       <c r="F833" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G833" t="inlineStr">
         <is>
@@ -28773,7 +28773,7 @@
     <row r="834">
       <c r="A834" t="inlineStr">
         <is>
-          <t>Bayern (Regular)</t>
+          <t>Hessen (Regular)</t>
         </is>
       </c>
       <c r="B834" t="inlineStr">
@@ -28782,16 +28782,16 @@
         </is>
       </c>
       <c r="C834" t="n">
-        <v>2186</v>
+        <v>0</v>
       </c>
       <c r="D834" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="E834" t="n">
-        <v>15199</v>
+        <v>0</v>
       </c>
       <c r="F834" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G834" t="inlineStr">
         <is>
@@ -28807,7 +28807,7 @@
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>Bayern (Regular)</t>
+          <t>Hessen (Regular)</t>
         </is>
       </c>
       <c r="B835" t="inlineStr">
@@ -28816,16 +28816,16 @@
         </is>
       </c>
       <c r="C835" t="n">
-        <v>64000</v>
+        <v>17024</v>
       </c>
       <c r="D835" t="n">
-        <v>74.7</v>
+        <v>63.6</v>
       </c>
       <c r="E835" t="n">
-        <v>11927069</v>
+        <v>5520014</v>
       </c>
       <c r="F835" t="n">
-        <v>89.90000000000001</v>
+        <v>88.3</v>
       </c>
       <c r="G835" t="inlineStr">
         <is>
@@ -28841,7 +28841,7 @@
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>Bayern (Extended)</t>
+          <t>Hessen (Extended)</t>
         </is>
       </c>
       <c r="B836" t="inlineStr">
@@ -28850,16 +28850,16 @@
         </is>
       </c>
       <c r="C836" t="n">
-        <v>46</v>
+        <v>383</v>
       </c>
       <c r="D836" t="n">
-        <v>0.1</v>
+        <v>1.4</v>
       </c>
       <c r="E836" t="n">
-        <v>1725</v>
+        <v>14258</v>
       </c>
       <c r="F836" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G836" t="inlineStr">
         <is>
@@ -28875,7 +28875,7 @@
     <row r="837">
       <c r="A837" t="inlineStr">
         <is>
-          <t>Bayern (Extended)</t>
+          <t>Hessen (Extended)</t>
         </is>
       </c>
       <c r="B837" t="inlineStr">
@@ -28884,16 +28884,16 @@
         </is>
       </c>
       <c r="C837" t="n">
-        <v>2573</v>
+        <v>1494</v>
       </c>
       <c r="D837" t="n">
-        <v>3</v>
+        <v>5.6</v>
       </c>
       <c r="E837" t="n">
-        <v>149995</v>
+        <v>105358</v>
       </c>
       <c r="F837" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="G837" t="inlineStr">
         <is>
@@ -28909,7 +28909,7 @@
     <row r="838">
       <c r="A838" t="inlineStr">
         <is>
-          <t>Bayern (Extended)</t>
+          <t>Hessen (Extended)</t>
         </is>
       </c>
       <c r="B838" t="inlineStr">
@@ -28918,16 +28918,16 @@
         </is>
       </c>
       <c r="C838" t="n">
-        <v>13459</v>
+        <v>4886</v>
       </c>
       <c r="D838" t="n">
-        <v>15.7</v>
+        <v>18.3</v>
       </c>
       <c r="E838" t="n">
-        <v>913302</v>
+        <v>349316</v>
       </c>
       <c r="F838" t="n">
-        <v>6.9</v>
+        <v>5.6</v>
       </c>
       <c r="G838" t="inlineStr">
         <is>
@@ -28943,7 +28943,7 @@
     <row r="839">
       <c r="A839" t="inlineStr">
         <is>
-          <t>Bayern (Extended)</t>
+          <t>Hessen (Extended)</t>
         </is>
       </c>
       <c r="B839" t="inlineStr">
@@ -28952,13 +28952,13 @@
         </is>
       </c>
       <c r="C839" t="n">
-        <v>78</v>
+        <v>37</v>
       </c>
       <c r="D839" t="n">
         <v>0.1</v>
       </c>
       <c r="E839" t="n">
-        <v>2189</v>
+        <v>677</v>
       </c>
       <c r="F839" t="n">
         <v>0</v>
@@ -28977,7 +28977,7 @@
     <row r="840">
       <c r="A840" t="inlineStr">
         <is>
-          <t>Bayern (Extended)</t>
+          <t>Hessen (Extended)</t>
         </is>
       </c>
       <c r="B840" t="inlineStr">
@@ -28986,16 +28986,16 @@
         </is>
       </c>
       <c r="C840" t="n">
-        <v>2186</v>
+        <v>0</v>
       </c>
       <c r="D840" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="E840" t="n">
-        <v>15199</v>
+        <v>0</v>
       </c>
       <c r="F840" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G840" t="inlineStr">
         <is>
@@ -29011,7 +29011,7 @@
     <row r="841">
       <c r="A841" t="inlineStr">
         <is>
-          <t>Bayern (Extended)</t>
+          <t>Hessen (Extended)</t>
         </is>
       </c>
       <c r="B841" t="inlineStr">
@@ -29020,16 +29020,16 @@
         </is>
       </c>
       <c r="C841" t="n">
-        <v>67351</v>
+        <v>19948</v>
       </c>
       <c r="D841" t="n">
-        <v>78.59999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="E841" t="n">
-        <v>12188720</v>
+        <v>5784801</v>
       </c>
       <c r="F841" t="n">
-        <v>91.8</v>
+        <v>92.5</v>
       </c>
       <c r="G841" t="inlineStr">
         <is>
@@ -29045,7 +29045,7 @@
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t>Hessen (Regular)</t>
+          <t>Bayern (Regular)</t>
         </is>
       </c>
       <c r="B842" t="inlineStr">
@@ -29054,16 +29054,16 @@
         </is>
       </c>
       <c r="C842" t="n">
-        <v>729</v>
+        <v>230</v>
       </c>
       <c r="D842" t="n">
-        <v>2.7</v>
+        <v>0.3</v>
       </c>
       <c r="E842" t="n">
-        <v>46046</v>
+        <v>9712</v>
       </c>
       <c r="F842" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="G842" t="inlineStr">
         <is>
@@ -29079,7 +29079,7 @@
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
-          <t>Hessen (Regular)</t>
+          <t>Bayern (Regular)</t>
         </is>
       </c>
       <c r="B843" t="inlineStr">
@@ -29088,16 +29088,16 @@
         </is>
       </c>
       <c r="C843" t="n">
-        <v>3014</v>
+        <v>3511</v>
       </c>
       <c r="D843" t="n">
-        <v>11.3</v>
+        <v>4.1</v>
       </c>
       <c r="E843" t="n">
-        <v>193787</v>
+        <v>197929</v>
       </c>
       <c r="F843" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="G843" t="inlineStr">
         <is>
@@ -29113,7 +29113,7 @@
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t>Hessen (Regular)</t>
+          <t>Bayern (Regular)</t>
         </is>
       </c>
       <c r="B844" t="inlineStr">
@@ -29122,16 +29122,16 @@
         </is>
       </c>
       <c r="C844" t="n">
-        <v>5796</v>
+        <v>15607</v>
       </c>
       <c r="D844" t="n">
-        <v>21.7</v>
+        <v>18.2</v>
       </c>
       <c r="E844" t="n">
-        <v>488536</v>
+        <v>1118370</v>
       </c>
       <c r="F844" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="G844" t="inlineStr">
         <is>
@@ -29147,7 +29147,7 @@
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>Hessen (Regular)</t>
+          <t>Bayern (Regular)</t>
         </is>
       </c>
       <c r="B845" t="inlineStr">
@@ -29156,16 +29156,16 @@
         </is>
       </c>
       <c r="C845" t="n">
-        <v>185</v>
+        <v>159</v>
       </c>
       <c r="D845" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="E845" t="n">
-        <v>6027</v>
+        <v>2851</v>
       </c>
       <c r="F845" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G845" t="inlineStr">
         <is>
@@ -29181,7 +29181,7 @@
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>Hessen (Regular)</t>
+          <t>Bayern (Regular)</t>
         </is>
       </c>
       <c r="B846" t="inlineStr">
@@ -29190,16 +29190,16 @@
         </is>
       </c>
       <c r="C846" t="n">
-        <v>0</v>
+        <v>2186</v>
       </c>
       <c r="D846" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="E846" t="n">
-        <v>0</v>
+        <v>15199</v>
       </c>
       <c r="F846" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G846" t="inlineStr">
         <is>
@@ -29215,7 +29215,7 @@
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>Hessen (Regular)</t>
+          <t>Bayern (Regular)</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
@@ -29224,16 +29224,16 @@
         </is>
       </c>
       <c r="C847" t="n">
-        <v>17024</v>
+        <v>64000</v>
       </c>
       <c r="D847" t="n">
-        <v>63.6</v>
+        <v>74.7</v>
       </c>
       <c r="E847" t="n">
-        <v>5520014</v>
+        <v>11927069</v>
       </c>
       <c r="F847" t="n">
-        <v>88.3</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="G847" t="inlineStr">
         <is>
@@ -29249,7 +29249,7 @@
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>Hessen (Extended)</t>
+          <t>Bayern (Extended)</t>
         </is>
       </c>
       <c r="B848" t="inlineStr">
@@ -29258,16 +29258,16 @@
         </is>
       </c>
       <c r="C848" t="n">
-        <v>383</v>
+        <v>46</v>
       </c>
       <c r="D848" t="n">
-        <v>1.4</v>
+        <v>0.1</v>
       </c>
       <c r="E848" t="n">
-        <v>14258</v>
+        <v>1725</v>
       </c>
       <c r="F848" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G848" t="inlineStr">
         <is>
@@ -29283,7 +29283,7 @@
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>Hessen (Extended)</t>
+          <t>Bayern (Extended)</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
@@ -29292,16 +29292,16 @@
         </is>
       </c>
       <c r="C849" t="n">
-        <v>1494</v>
+        <v>2573</v>
       </c>
       <c r="D849" t="n">
-        <v>5.6</v>
+        <v>3</v>
       </c>
       <c r="E849" t="n">
-        <v>105358</v>
+        <v>149995</v>
       </c>
       <c r="F849" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="G849" t="inlineStr">
         <is>
@@ -29317,7 +29317,7 @@
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>Hessen (Extended)</t>
+          <t>Bayern (Extended)</t>
         </is>
       </c>
       <c r="B850" t="inlineStr">
@@ -29326,16 +29326,16 @@
         </is>
       </c>
       <c r="C850" t="n">
-        <v>4886</v>
+        <v>13459</v>
       </c>
       <c r="D850" t="n">
-        <v>18.3</v>
+        <v>15.7</v>
       </c>
       <c r="E850" t="n">
-        <v>349316</v>
+        <v>913302</v>
       </c>
       <c r="F850" t="n">
-        <v>5.6</v>
+        <v>6.9</v>
       </c>
       <c r="G850" t="inlineStr">
         <is>
@@ -29351,7 +29351,7 @@
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t>Hessen (Extended)</t>
+          <t>Bayern (Extended)</t>
         </is>
       </c>
       <c r="B851" t="inlineStr">
@@ -29360,13 +29360,13 @@
         </is>
       </c>
       <c r="C851" t="n">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="D851" t="n">
         <v>0.1</v>
       </c>
       <c r="E851" t="n">
-        <v>677</v>
+        <v>2189</v>
       </c>
       <c r="F851" t="n">
         <v>0</v>
@@ -29385,7 +29385,7 @@
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t>Hessen (Extended)</t>
+          <t>Bayern (Extended)</t>
         </is>
       </c>
       <c r="B852" t="inlineStr">
@@ -29394,16 +29394,16 @@
         </is>
       </c>
       <c r="C852" t="n">
-        <v>0</v>
+        <v>2186</v>
       </c>
       <c r="D852" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="E852" t="n">
-        <v>0</v>
+        <v>15199</v>
       </c>
       <c r="F852" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G852" t="inlineStr">
         <is>
@@ -29419,7 +29419,7 @@
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>Hessen (Extended)</t>
+          <t>Bayern (Extended)</t>
         </is>
       </c>
       <c r="B853" t="inlineStr">
@@ -29428,16 +29428,16 @@
         </is>
       </c>
       <c r="C853" t="n">
-        <v>19948</v>
+        <v>67351</v>
       </c>
       <c r="D853" t="n">
-        <v>74.59999999999999</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="E853" t="n">
-        <v>5784801</v>
+        <v>12188720</v>
       </c>
       <c r="F853" t="n">
-        <v>92.5</v>
+        <v>91.8</v>
       </c>
       <c r="G853" t="inlineStr">
         <is>
@@ -31493,7 +31493,7 @@
     <row r="914">
       <c r="A914" t="inlineStr">
         <is>
-          <t>Sachsen-Anhalt (Regular)</t>
+          <t>Sachsen (Regular)</t>
         </is>
       </c>
       <c r="B914" t="inlineStr">
@@ -31502,16 +31502,16 @@
         </is>
       </c>
       <c r="C914" t="n">
-        <v>2649</v>
+        <v>1003</v>
       </c>
       <c r="D914" t="n">
-        <v>9.800000000000001</v>
+        <v>4.3</v>
       </c>
       <c r="E914" t="n">
-        <v>125398</v>
+        <v>84723</v>
       </c>
       <c r="F914" t="n">
-        <v>6</v>
+        <v>2.1</v>
       </c>
       <c r="G914" t="inlineStr">
         <is>
@@ -31527,7 +31527,7 @@
     <row r="915">
       <c r="A915" t="inlineStr">
         <is>
-          <t>Sachsen-Anhalt (Regular)</t>
+          <t>Sachsen (Regular)</t>
         </is>
       </c>
       <c r="B915" t="inlineStr">
@@ -31536,16 +31536,16 @@
         </is>
       </c>
       <c r="C915" t="n">
-        <v>4117</v>
+        <v>2933</v>
       </c>
       <c r="D915" t="n">
-        <v>15.3</v>
+        <v>12.6</v>
       </c>
       <c r="E915" t="n">
-        <v>213634</v>
+        <v>248159</v>
       </c>
       <c r="F915" t="n">
-        <v>10.2</v>
+        <v>6.1</v>
       </c>
       <c r="G915" t="inlineStr">
         <is>
@@ -31561,7 +31561,7 @@
     <row r="916">
       <c r="A916" t="inlineStr">
         <is>
-          <t>Sachsen-Anhalt (Regular)</t>
+          <t>Sachsen (Regular)</t>
         </is>
       </c>
       <c r="B916" t="inlineStr">
@@ -31570,16 +31570,16 @@
         </is>
       </c>
       <c r="C916" t="n">
-        <v>6058</v>
+        <v>5739</v>
       </c>
       <c r="D916" t="n">
-        <v>22.5</v>
+        <v>24.7</v>
       </c>
       <c r="E916" t="n">
-        <v>402134</v>
+        <v>539436</v>
       </c>
       <c r="F916" t="n">
-        <v>19.1</v>
+        <v>13.2</v>
       </c>
       <c r="G916" t="inlineStr">
         <is>
@@ -31595,7 +31595,7 @@
     <row r="917">
       <c r="A917" t="inlineStr">
         <is>
-          <t>Sachsen-Anhalt (Regular)</t>
+          <t>Sachsen (Regular)</t>
         </is>
       </c>
       <c r="B917" t="inlineStr">
@@ -31604,16 +31604,16 @@
         </is>
       </c>
       <c r="C917" t="n">
-        <v>5810</v>
+        <v>441</v>
       </c>
       <c r="D917" t="n">
-        <v>21.6</v>
+        <v>1.9</v>
       </c>
       <c r="E917" t="n">
-        <v>139112</v>
+        <v>19215</v>
       </c>
       <c r="F917" t="n">
-        <v>6.6</v>
+        <v>0.5</v>
       </c>
       <c r="G917" t="inlineStr">
         <is>
@@ -31629,7 +31629,7 @@
     <row r="918">
       <c r="A918" t="inlineStr">
         <is>
-          <t>Sachsen-Anhalt (Regular)</t>
+          <t>Sachsen (Regular)</t>
         </is>
       </c>
       <c r="B918" t="inlineStr">
@@ -31638,13 +31638,13 @@
         </is>
       </c>
       <c r="C918" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="D918" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="E918" t="n">
-        <v>0</v>
+        <v>655</v>
       </c>
       <c r="F918" t="n">
         <v>0</v>
@@ -31663,7 +31663,7 @@
     <row r="919">
       <c r="A919" t="inlineStr">
         <is>
-          <t>Sachsen-Anhalt (Regular)</t>
+          <t>Sachsen (Regular)</t>
         </is>
       </c>
       <c r="B919" t="inlineStr">
@@ -31672,16 +31672,16 @@
         </is>
       </c>
       <c r="C919" t="n">
-        <v>8302</v>
+        <v>13032</v>
       </c>
       <c r="D919" t="n">
-        <v>30.8</v>
+        <v>56</v>
       </c>
       <c r="E919" t="n">
-        <v>1222936</v>
+        <v>3187317</v>
       </c>
       <c r="F919" t="n">
-        <v>58.1</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="G919" t="inlineStr">
         <is>
@@ -31697,7 +31697,7 @@
     <row r="920">
       <c r="A920" t="inlineStr">
         <is>
-          <t>Sachsen-Anhalt (Extended)</t>
+          <t>Sachsen (Extended)</t>
         </is>
       </c>
       <c r="B920" t="inlineStr">
@@ -31706,16 +31706,16 @@
         </is>
       </c>
       <c r="C920" t="n">
-        <v>1709</v>
+        <v>511</v>
       </c>
       <c r="D920" t="n">
-        <v>6.3</v>
+        <v>2.2</v>
       </c>
       <c r="E920" t="n">
-        <v>62270</v>
+        <v>52465</v>
       </c>
       <c r="F920" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="G920" t="inlineStr">
         <is>
@@ -31731,7 +31731,7 @@
     <row r="921">
       <c r="A921" t="inlineStr">
         <is>
-          <t>Sachsen-Anhalt (Extended)</t>
+          <t>Sachsen (Extended)</t>
         </is>
       </c>
       <c r="B921" t="inlineStr">
@@ -31740,16 +31740,16 @@
         </is>
       </c>
       <c r="C921" t="n">
-        <v>3602</v>
+        <v>2209</v>
       </c>
       <c r="D921" t="n">
-        <v>13.4</v>
+        <v>9.5</v>
       </c>
       <c r="E921" t="n">
-        <v>88973</v>
+        <v>174023</v>
       </c>
       <c r="F921" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="G921" t="inlineStr">
         <is>
@@ -31765,7 +31765,7 @@
     <row r="922">
       <c r="A922" t="inlineStr">
         <is>
-          <t>Sachsen-Anhalt (Extended)</t>
+          <t>Sachsen (Extended)</t>
         </is>
       </c>
       <c r="B922" t="inlineStr">
@@ -31774,16 +31774,16 @@
         </is>
       </c>
       <c r="C922" t="n">
-        <v>6069</v>
+        <v>5267</v>
       </c>
       <c r="D922" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="E922" t="n">
-        <v>292512</v>
+        <v>433290</v>
       </c>
       <c r="F922" t="n">
-        <v>13.9</v>
+        <v>10.6</v>
       </c>
       <c r="G922" t="inlineStr">
         <is>
@@ -31799,7 +31799,7 @@
     <row r="923">
       <c r="A923" t="inlineStr">
         <is>
-          <t>Sachsen-Anhalt (Extended)</t>
+          <t>Sachsen (Extended)</t>
         </is>
       </c>
       <c r="B923" t="inlineStr">
@@ -31808,16 +31808,16 @@
         </is>
       </c>
       <c r="C923" t="n">
-        <v>1546</v>
+        <v>157</v>
       </c>
       <c r="D923" t="n">
-        <v>5.7</v>
+        <v>0.7</v>
       </c>
       <c r="E923" t="n">
-        <v>19488</v>
+        <v>6222</v>
       </c>
       <c r="F923" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="G923" t="inlineStr">
         <is>
@@ -31833,7 +31833,7 @@
     <row r="924">
       <c r="A924" t="inlineStr">
         <is>
-          <t>Sachsen-Anhalt (Extended)</t>
+          <t>Sachsen (Extended)</t>
         </is>
       </c>
       <c r="B924" t="inlineStr">
@@ -31842,13 +31842,13 @@
         </is>
       </c>
       <c r="C924" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="D924" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="E924" t="n">
-        <v>0</v>
+        <v>656</v>
       </c>
       <c r="F924" t="n">
         <v>0</v>
@@ -31867,7 +31867,7 @@
     <row r="925">
       <c r="A925" t="inlineStr">
         <is>
-          <t>Sachsen-Anhalt (Extended)</t>
+          <t>Sachsen (Extended)</t>
         </is>
       </c>
       <c r="B925" t="inlineStr">
@@ -31876,16 +31876,16 @@
         </is>
       </c>
       <c r="C925" t="n">
-        <v>14010</v>
+        <v>15006</v>
       </c>
       <c r="D925" t="n">
-        <v>52</v>
+        <v>64.5</v>
       </c>
       <c r="E925" t="n">
-        <v>1639971</v>
+        <v>3412849</v>
       </c>
       <c r="F925" t="n">
-        <v>78</v>
+        <v>83.7</v>
       </c>
       <c r="G925" t="inlineStr">
         <is>
@@ -31901,7 +31901,7 @@
     <row r="926">
       <c r="A926" t="inlineStr">
         <is>
-          <t>Sachsen (Regular)</t>
+          <t>Sachsen-Anhalt (Regular)</t>
         </is>
       </c>
       <c r="B926" t="inlineStr">
@@ -31910,16 +31910,16 @@
         </is>
       </c>
       <c r="C926" t="n">
-        <v>1003</v>
+        <v>2649</v>
       </c>
       <c r="D926" t="n">
-        <v>4.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E926" t="n">
-        <v>84723</v>
+        <v>125398</v>
       </c>
       <c r="F926" t="n">
-        <v>2.1</v>
+        <v>6</v>
       </c>
       <c r="G926" t="inlineStr">
         <is>
@@ -31935,7 +31935,7 @@
     <row r="927">
       <c r="A927" t="inlineStr">
         <is>
-          <t>Sachsen (Regular)</t>
+          <t>Sachsen-Anhalt (Regular)</t>
         </is>
       </c>
       <c r="B927" t="inlineStr">
@@ -31944,16 +31944,16 @@
         </is>
       </c>
       <c r="C927" t="n">
-        <v>2933</v>
+        <v>4117</v>
       </c>
       <c r="D927" t="n">
-        <v>12.6</v>
+        <v>15.3</v>
       </c>
       <c r="E927" t="n">
-        <v>248159</v>
+        <v>213634</v>
       </c>
       <c r="F927" t="n">
-        <v>6.1</v>
+        <v>10.2</v>
       </c>
       <c r="G927" t="inlineStr">
         <is>
@@ -31969,7 +31969,7 @@
     <row r="928">
       <c r="A928" t="inlineStr">
         <is>
-          <t>Sachsen (Regular)</t>
+          <t>Sachsen-Anhalt (Regular)</t>
         </is>
       </c>
       <c r="B928" t="inlineStr">
@@ -31978,16 +31978,16 @@
         </is>
       </c>
       <c r="C928" t="n">
-        <v>5739</v>
+        <v>6058</v>
       </c>
       <c r="D928" t="n">
-        <v>24.7</v>
+        <v>22.5</v>
       </c>
       <c r="E928" t="n">
-        <v>539436</v>
+        <v>402134</v>
       </c>
       <c r="F928" t="n">
-        <v>13.2</v>
+        <v>19.1</v>
       </c>
       <c r="G928" t="inlineStr">
         <is>
@@ -32003,7 +32003,7 @@
     <row r="929">
       <c r="A929" t="inlineStr">
         <is>
-          <t>Sachsen (Regular)</t>
+          <t>Sachsen-Anhalt (Regular)</t>
         </is>
       </c>
       <c r="B929" t="inlineStr">
@@ -32012,16 +32012,16 @@
         </is>
       </c>
       <c r="C929" t="n">
-        <v>441</v>
+        <v>5810</v>
       </c>
       <c r="D929" t="n">
-        <v>1.9</v>
+        <v>21.6</v>
       </c>
       <c r="E929" t="n">
-        <v>19215</v>
+        <v>139112</v>
       </c>
       <c r="F929" t="n">
-        <v>0.5</v>
+        <v>6.6</v>
       </c>
       <c r="G929" t="inlineStr">
         <is>
@@ -32037,7 +32037,7 @@
     <row r="930">
       <c r="A930" t="inlineStr">
         <is>
-          <t>Sachsen (Regular)</t>
+          <t>Sachsen-Anhalt (Regular)</t>
         </is>
       </c>
       <c r="B930" t="inlineStr">
@@ -32046,13 +32046,13 @@
         </is>
       </c>
       <c r="C930" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="D930" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="E930" t="n">
-        <v>655</v>
+        <v>0</v>
       </c>
       <c r="F930" t="n">
         <v>0</v>
@@ -32071,7 +32071,7 @@
     <row r="931">
       <c r="A931" t="inlineStr">
         <is>
-          <t>Sachsen (Regular)</t>
+          <t>Sachsen-Anhalt (Regular)</t>
         </is>
       </c>
       <c r="B931" t="inlineStr">
@@ -32080,16 +32080,16 @@
         </is>
       </c>
       <c r="C931" t="n">
-        <v>13032</v>
+        <v>8302</v>
       </c>
       <c r="D931" t="n">
-        <v>56</v>
+        <v>30.8</v>
       </c>
       <c r="E931" t="n">
-        <v>3187317</v>
+        <v>1222936</v>
       </c>
       <c r="F931" t="n">
-        <v>78.09999999999999</v>
+        <v>58.1</v>
       </c>
       <c r="G931" t="inlineStr">
         <is>
@@ -32105,7 +32105,7 @@
     <row r="932">
       <c r="A932" t="inlineStr">
         <is>
-          <t>Sachsen (Extended)</t>
+          <t>Sachsen-Anhalt (Extended)</t>
         </is>
       </c>
       <c r="B932" t="inlineStr">
@@ -32114,16 +32114,16 @@
         </is>
       </c>
       <c r="C932" t="n">
-        <v>511</v>
+        <v>1709</v>
       </c>
       <c r="D932" t="n">
-        <v>2.2</v>
+        <v>6.3</v>
       </c>
       <c r="E932" t="n">
-        <v>52465</v>
+        <v>62270</v>
       </c>
       <c r="F932" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="G932" t="inlineStr">
         <is>
@@ -32139,7 +32139,7 @@
     <row r="933">
       <c r="A933" t="inlineStr">
         <is>
-          <t>Sachsen (Extended)</t>
+          <t>Sachsen-Anhalt (Extended)</t>
         </is>
       </c>
       <c r="B933" t="inlineStr">
@@ -32148,16 +32148,16 @@
         </is>
       </c>
       <c r="C933" t="n">
-        <v>2209</v>
+        <v>3602</v>
       </c>
       <c r="D933" t="n">
-        <v>9.5</v>
+        <v>13.4</v>
       </c>
       <c r="E933" t="n">
-        <v>174023</v>
+        <v>88973</v>
       </c>
       <c r="F933" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="G933" t="inlineStr">
         <is>
@@ -32173,7 +32173,7 @@
     <row r="934">
       <c r="A934" t="inlineStr">
         <is>
-          <t>Sachsen (Extended)</t>
+          <t>Sachsen-Anhalt (Extended)</t>
         </is>
       </c>
       <c r="B934" t="inlineStr">
@@ -32182,16 +32182,16 @@
         </is>
       </c>
       <c r="C934" t="n">
-        <v>5267</v>
+        <v>6069</v>
       </c>
       <c r="D934" t="n">
-        <v>22.7</v>
+        <v>22.5</v>
       </c>
       <c r="E934" t="n">
-        <v>433290</v>
+        <v>292512</v>
       </c>
       <c r="F934" t="n">
-        <v>10.6</v>
+        <v>13.9</v>
       </c>
       <c r="G934" t="inlineStr">
         <is>
@@ -32207,7 +32207,7 @@
     <row r="935">
       <c r="A935" t="inlineStr">
         <is>
-          <t>Sachsen (Extended)</t>
+          <t>Sachsen-Anhalt (Extended)</t>
         </is>
       </c>
       <c r="B935" t="inlineStr">
@@ -32216,16 +32216,16 @@
         </is>
       </c>
       <c r="C935" t="n">
-        <v>157</v>
+        <v>1546</v>
       </c>
       <c r="D935" t="n">
-        <v>0.7</v>
+        <v>5.7</v>
       </c>
       <c r="E935" t="n">
-        <v>6222</v>
+        <v>19488</v>
       </c>
       <c r="F935" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="G935" t="inlineStr">
         <is>
@@ -32241,7 +32241,7 @@
     <row r="936">
       <c r="A936" t="inlineStr">
         <is>
-          <t>Sachsen (Extended)</t>
+          <t>Sachsen-Anhalt (Extended)</t>
         </is>
       </c>
       <c r="B936" t="inlineStr">
@@ -32250,13 +32250,13 @@
         </is>
       </c>
       <c r="C936" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="D936" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="E936" t="n">
-        <v>656</v>
+        <v>0</v>
       </c>
       <c r="F936" t="n">
         <v>0</v>
@@ -32275,7 +32275,7 @@
     <row r="937">
       <c r="A937" t="inlineStr">
         <is>
-          <t>Sachsen (Extended)</t>
+          <t>Sachsen-Anhalt (Extended)</t>
         </is>
       </c>
       <c r="B937" t="inlineStr">
@@ -32284,16 +32284,16 @@
         </is>
       </c>
       <c r="C937" t="n">
-        <v>15006</v>
+        <v>14010</v>
       </c>
       <c r="D937" t="n">
-        <v>64.5</v>
+        <v>52</v>
       </c>
       <c r="E937" t="n">
-        <v>3412849</v>
+        <v>1639971</v>
       </c>
       <c r="F937" t="n">
-        <v>83.7</v>
+        <v>78</v>
       </c>
       <c r="G937" t="inlineStr">
         <is>
